--- a/outputs/china_liquor_batch.xlsx
+++ b/outputs/china_liquor_batch.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主体任务'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'横向比较'!$A$1:$Z$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'版本信息'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'横向比较'!$A$1:$AB$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'版本信息'!$A$1:$C$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -619,7 +619,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -802,12 +802,14 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="25" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="52" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="25" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,25 +920,35 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>selected_model_version</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>forecast_candidate_models</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>selected_forecast_close</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>forecast_lower_bound</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>forecast_upper_bound</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>cross_validation_status</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -1019,24 +1031,34 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>last_close_baseline</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>1330</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <v>1293.474</v>
+          <t>historical_mean_baseline</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>historical-mean-v1</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>last_close_baseline, moving_average_baseline, historical_mean_baseline, exponential_smoothing_baseline, multisignal_ridge</t>
+        </is>
       </c>
       <c r="X2" s="3" t="n">
-        <v>1366.526</v>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
+        <v>1329.739493643314</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>1292.777006813398</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>1366.70198047323</v>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
@@ -1119,31 +1141,41 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>last_close_baseline</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>71.98</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>70.056</v>
+          <t>historical_mean_baseline</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>historical-mean-v1</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>last_close_baseline, moving_average_baseline, historical_mean_baseline, exponential_smoothing_baseline, multisignal_ridge</t>
+        </is>
       </c>
       <c r="X3" s="3" t="n">
-        <v>73.90400000000001</v>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
+        <v>71.92511982887757</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>70.0556205710019</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>73.79461908675324</v>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z3"/>
+  <autoFilter ref="A1:AB3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1154,11 +1186,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1187,7 +1219,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1204,7 +1236,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1221,7 +1253,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1255,7 +1287,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1272,7 +1304,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1301,22 +1333,73 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>moving_average_baseline</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>moving-average-v1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>central version registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>historical_mean_baseline</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>historical-mean-v1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>central version registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>exponential_smoothing_baseline</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ewma-v1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>central version registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>multisignal_ridge</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>ridge-v1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>central version registry</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9"/>
+  <autoFilter ref="A1:C12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>